--- a/travel/2026-11_JANES/学会出席等出張許可申請書_11月7日_北ヨーロッパ学会.xlsx
+++ b/travel/2026-11_JANES/学会出席等出張許可申請書_11月7日_北ヨーロッパ学会.xlsx
@@ -624,10 +624,11 @@
   </si>
   <si>
     <t xml:space="preserve">北ヨーロッパ学会 2026年度研究大会・総会
-（共通論題「北欧学の新展開」）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">東海大学 品川キャンパス
+自由論題にて研究報告（セッション②「環境」10:30～12:10）
+報告題目：「マンカラ原則とフィンランド自治体エネルギー事業―北欧比較からみる自治体財政基盤の形成」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">東海大学 品川キャンパス 4号館
 （東京都港区高輪2-3-23）</t>
   </si>
   <si>
@@ -1468,14 +1469,14 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>174625</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>98425</xdr:rowOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>12699</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>374650</xdr:rowOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>457200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
